--- a/artfynd/S 617-2023 artfynd.xlsx
+++ b/artfynd/S 617-2023 artfynd.xlsx
@@ -2101,7 +2101,7 @@
         <v>136498571</v>
       </c>
       <c r="B14" t="n">
-        <v>57193</v>
+        <v>57195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
